--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$22</f>
+              <f>'30日跟踪'!$A$8:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$22</f>
+              <f>'30日跟踪'!$D$8:$D$24</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="7">
@@ -988,6 +988,46 @@
       <c r="E22" t="inlineStr">
         <is>
           <t>第15/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>68.12000274658203</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>2.466906297888127</v>
+      </c>
+      <c r="D23" s="6">
+        <f>B23/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>第16/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>7.163824217054704</v>
+      </c>
+      <c r="D24" s="6">
+        <f>B24/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>第17/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$24</f>
+              <f>'30日跟踪'!$A$8:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$24</f>
+              <f>'30日跟踪'!$D$8:$D$25</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1031,6 +1031,26 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>74.31999969482422</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>1.808218760033187</v>
+      </c>
+      <c r="D25" s="6">
+        <f>B25/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>第18/30个交易日</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$25</f>
+              <f>'30日跟踪'!$A$8:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$25</f>
+              <f>'30日跟踪'!$D$8:$D$26</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="7">
@@ -1048,6 +1048,26 @@
       <c r="E25" t="inlineStr">
         <is>
           <t>第18/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>74.59999847412109</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>0.3767475517311825</v>
+      </c>
+      <c r="D26" s="6">
+        <f>B26/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>第19/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$26</f>
+              <f>'30日跟踪'!$A$8:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$26</f>
+              <f>'30日跟踪'!$D$8:$D$27</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="7">
@@ -1068,6 +1068,26 @@
       <c r="E26" t="inlineStr">
         <is>
           <t>第19/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>-2.479890766704052</v>
+      </c>
+      <c r="D27" s="6">
+        <f>B27/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>第20/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$27</f>
+              <f>'30日跟踪'!$A$8:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$27</f>
+              <f>'30日跟踪'!$D$8:$D$29</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="7">
@@ -1088,6 +1088,46 @@
       <c r="E27" t="inlineStr">
         <is>
           <t>第20/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>72.73999786376953</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>-0.01374864086662875</v>
+      </c>
+      <c r="D28" s="6">
+        <f>B28/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>第21/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>76.77999877929688</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>5.554029466832855</v>
+      </c>
+      <c r="D29" s="6">
+        <f>B29/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>第22/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$29</f>
+              <f>'30日跟踪'!$A$8:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$29</f>
+              <f>'30日跟踪'!$D$8:$D$30</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="7">
@@ -1128,6 +1128,26 @@
       <c r="E29" t="inlineStr">
         <is>
           <t>第22/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>75.72000122070312</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>-1.380564698419307</v>
+      </c>
+      <c r="D30" s="6">
+        <f>B30/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>第23/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$30</f>
+              <f>'30日跟踪'!$A$8:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$30</f>
+              <f>'30日跟踪'!$D$8:$D$32</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="7">
@@ -1148,6 +1148,46 @@
       <c r="E30" t="inlineStr">
         <is>
           <t>第23/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>69.05999755859375</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>-8.795567293636564</v>
+      </c>
+      <c r="D31" s="6">
+        <f>B31/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>第24/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>68.80999755859375</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>-0.3620040672429603</v>
+      </c>
+      <c r="D32" s="6">
+        <f>B32/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>第25/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$32</f>
+              <f>'30日跟踪'!$A$8:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$32</f>
+              <f>'30日跟踪'!$D$8:$D$34</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="7">
@@ -1153,13 +1153,13 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B31" s="4" t="n">
-        <v>69.05999755859375</v>
+        <v>71.30000305175781</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-8.795567293636564</v>
+        <v>-5.83729278617181</v>
       </c>
       <c r="D31" s="6">
         <f>B31/$B$8-1</f>
@@ -1173,13 +1173,13 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B32" s="4" t="n">
-        <v>68.80999755859375</v>
+        <v>69.05999755859375</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.3620040672429603</v>
+        <v>-3.141662548791202</v>
       </c>
       <c r="D32" s="6">
         <f>B32/$B$8-1</f>
@@ -1188,6 +1188,46 @@
       <c r="E32" t="inlineStr">
         <is>
           <t>第25/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>68.80999755859375</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>-0.3620040672429603</v>
+      </c>
+      <c r="D33" s="6">
+        <f>B33/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>第26/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>2.456042001697734</v>
+      </c>
+      <c r="D34" s="6">
+        <f>B34/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>第27/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$34</f>
+              <f>'30日跟踪'!$A$8:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$34</f>
+              <f>'30日跟踪'!$D$8:$D$35</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="7">
@@ -1228,6 +1228,26 @@
       <c r="E34" t="inlineStr">
         <is>
           <t>第27/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>-0.7092198581560294</v>
+      </c>
+      <c r="D35" s="6">
+        <f>B35/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>第28/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$35</f>
+              <f>'30日跟踪'!$A$8:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$35</f>
+              <f>'30日跟踪'!$D$8:$D$36</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="7">
@@ -1248,6 +1248,26 @@
       <c r="E35" t="inlineStr">
         <is>
           <t>第28/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>73.18000030517578</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>4.542857578822534</v>
+      </c>
+      <c r="D36" s="6">
+        <f>B36/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>第29/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$36</f>
+              <f>'30日跟踪'!$A$8:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$36</f>
+              <f>'30日跟踪'!$D$8:$D$37</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="7">
@@ -1268,6 +1268,26 @@
       <c r="E36" t="inlineStr">
         <is>
           <t>第29/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>69.36000061035156</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>-5.22000502718506</v>
+      </c>
+      <c r="D37" s="6">
+        <f>B37/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>第30/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/INSP_1_20260819.xlsx
+++ b/data/CROSS/EXCLE/INSP_1_20260819.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="7">
